--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>ASPI</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -725,31 +726,37 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>800</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -769,16 +776,22 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>300</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -813,16 +826,22 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -857,8 +876,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +900,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -884,29 +911,29 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
       </c>
       <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,8 +946,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,8 +996,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1007,8 +1046,14 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1051,8 +1096,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,38 +1117,40 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,38 +1163,44 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-5900</v>
       </c>
       <c r="E18" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1213,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,37 +1237,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-1100</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1216,38 +1283,44 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-6900</v>
       </c>
       <c r="E21" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,8 +1333,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1269,22 +1348,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1304,38 +1383,44 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,8 +1433,14 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1359,20 +1450,20 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1392,8 +1483,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,38 +1533,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-4300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,38 +1583,44 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,8 +1633,14 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1683,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1733,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1783,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,37 +1833,43 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>1100</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1744,38 +1883,44 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1788,8 +1933,14 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,38 +1983,44 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,43 +2033,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1925,8 +2088,14 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2112,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,35 +2132,37 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2800</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2005,8 +2178,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2049,31 +2228,37 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2093,8 +2278,14 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2137,35 +2328,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,35 +2378,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F46" s="3">
         <v>2700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3600</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2225,8 +2428,14 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2269,35 +2478,41 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,31 +2528,37 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>3300</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2357,8 +2578,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2628,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,8 +2678,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2454,22 +2693,22 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2483,14 +2722,20 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,35 +2778,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>27500</v>
+      </c>
+      <c r="F54" s="3">
         <v>11900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,8 +2828,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2852,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,35 +2872,37 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2657,16 +2918,22 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2680,11 +2947,11 @@
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2701,35 +2968,41 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,35 +3018,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F60" s="3">
         <v>2600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F60" s="3">
-        <v>2000</v>
       </c>
       <c r="G60" s="3">
         <v>1900</v>
       </c>
       <c r="H60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,16 +3068,22 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>22200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2833,35 +3118,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>700</v>
       </c>
       <c r="H62" s="3">
         <v>700</v>
       </c>
       <c r="I62" s="3">
+        <v>700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>700</v>
+      </c>
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2877,8 +3168,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3218,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3268,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,35 +3318,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F66" s="3">
         <v>3200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3368,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3392,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3438,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3488,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3203,8 +3538,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,35 +3588,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-19700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-15500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-11200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-7600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-6200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-4300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3291,8 +3638,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3688,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3738,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,35 +3788,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F76" s="3">
         <v>8600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7400</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3838,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,43 +3888,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3560,38 +3943,44 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3604,8 +3993,14 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,31 +4017,33 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3666,8 +4063,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +4113,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +4163,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4213,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4263,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,38 +4313,44 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,8 +4363,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,43 +4387,45 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -3992,8 +4433,14 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4483,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,38 +4533,44 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4583,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,8 +4607,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4186,8 +4653,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4703,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4753,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,38 +4803,44 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>2200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,16 +4853,22 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -4380,20 +4877,20 @@
         <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4406,38 +4903,44 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4448,6 +4951,12 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,20 +733,23 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
@@ -758,8 +762,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -782,8 +786,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -791,11 +798,11 @@
         <v>600</v>
       </c>
       <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,20 +839,23 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,8 +892,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,41 +915,42 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -952,8 +966,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1002,8 +1019,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1052,8 +1072,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1125,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1119,41 +1145,42 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,20 +1196,23 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1195,15 +1225,15 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,8 +1249,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1239,19 +1272,20 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1265,14 +1299,14 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1289,20 +1323,23 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4000</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,15 +1352,15 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,20 +1376,23 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1365,8 +1405,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1389,41 +1429,44 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-4200</v>
       </c>
       <c r="F23" s="3">
         <v>-4200</v>
       </c>
       <c r="G23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H23" s="3">
         <v>-4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,8 +1482,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1450,8 +1496,8 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1465,8 +1511,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1489,8 +1535,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1539,41 +1588,44 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-4200</v>
       </c>
       <c r="F26" s="3">
         <v>-4200</v>
       </c>
       <c r="G26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,41 +1641,44 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-4200</v>
       </c>
       <c r="F27" s="3">
         <v>-4200</v>
       </c>
       <c r="G27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H27" s="3">
         <v>-4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1639,8 +1694,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,8 +1747,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,8 +1800,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1789,8 +1853,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1839,19 +1906,22 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1865,14 +1935,14 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1889,41 +1959,44 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-4200</v>
       </c>
       <c r="F33" s="3">
         <v>-4200</v>
       </c>
       <c r="G33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,8 +2012,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1989,41 +2065,44 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-4200</v>
       </c>
       <c r="F35" s="3">
         <v>-4200</v>
       </c>
       <c r="G35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,46 +2118,49 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2176,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2114,8 +2199,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2134,38 +2220,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E41" s="3">
         <v>23900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,8 +2271,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2234,20 +2324,23 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2260,8 +2353,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2284,8 +2377,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2334,38 +2430,41 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2384,38 +2483,41 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E46" s="3">
         <v>26200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2536,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2484,38 +2589,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E48" s="3">
         <v>15800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2534,20 +2642,23 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3300</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2560,8 +2671,8 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2584,8 +2695,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,8 +2748,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2684,8 +2801,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2693,16 +2813,16 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -2710,8 +2830,8 @@
       <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>100</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2728,14 +2848,17 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2784,38 +2907,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E54" s="3">
         <v>45400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,8 +2960,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2854,8 +2983,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2874,38 +3004,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,20 +3055,23 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -2953,8 +3087,8 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2974,38 +3108,41 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,38 +3161,41 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,20 +3214,23 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E61" s="3">
         <v>22200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -3124,25 +3267,28 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="E62" s="3">
         <v>2800</v>
       </c>
       <c r="F62" s="3">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="G62" s="3">
         <v>600</v>
       </c>
       <c r="H62" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I62" s="3">
         <v>700</v>
@@ -3151,11 +3297,11 @@
         <v>700</v>
       </c>
       <c r="K62" s="3">
+        <v>700</v>
+      </c>
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,8 +3320,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3224,8 +3373,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,8 +3426,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3324,38 +3479,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E66" s="3">
         <v>34900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>2700</v>
       </c>
       <c r="I66" s="3">
         <v>2700</v>
       </c>
       <c r="J66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2600</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,8 +3532,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3394,8 +3555,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,8 +3606,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3494,8 +3659,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3544,8 +3712,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3594,38 +3765,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-30800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-23800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-19700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3818,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3694,8 +3871,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3744,8 +3924,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3794,38 +3977,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,8 +4030,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3894,46 +4083,49 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3949,41 +4141,44 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-4200</v>
       </c>
       <c r="F81" s="3">
         <v>-4200</v>
       </c>
       <c r="G81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4194,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4019,8 +4217,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4028,10 +4227,10 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -4045,8 +4244,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4069,8 +4268,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4119,8 +4321,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4169,8 +4374,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4219,8 +4427,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4269,8 +4480,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4319,41 +4533,44 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4369,8 +4586,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4389,46 +4609,47 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4439,8 +4660,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4489,8 +4713,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4539,41 +4766,44 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +4819,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4609,8 +4842,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4659,8 +4893,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4709,8 +4946,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4759,8 +4999,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4809,41 +5052,44 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E100" s="3">
         <v>20300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8900</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>4500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3800</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4859,41 +5105,44 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4909,41 +5158,44 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E102" s="3">
         <v>16000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4957,6 +5209,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>ASPI</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -736,23 +737,26 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,8 +769,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -789,23 +793,26 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E9" s="3">
         <v>600</v>
       </c>
       <c r="F9" s="3">
+        <v>600</v>
+      </c>
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -842,23 +849,26 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3">
-        <v>200</v>
-      </c>
       <c r="F10" s="3">
+        <v>300</v>
+      </c>
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -895,8 +905,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -916,44 +929,45 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -969,8 +983,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1022,31 +1039,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1075,19 +1095,22 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1128,8 +1151,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1146,44 +1172,45 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E17" s="3">
         <v>8500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1199,44 +1226,47 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-5900</v>
-      </c>
       <c r="F18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-5800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3700</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1252,8 +1282,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1273,43 +1306,44 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1300</v>
+        <v>2400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1100</v>
+        <v>1400</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>1200</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1326,44 +1360,47 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4000</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-3600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,8 +1416,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1388,14 +1428,14 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1448,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1432,44 +1472,47 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4200</v>
       </c>
       <c r="G23" s="3">
         <v>-4200</v>
       </c>
       <c r="H23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1485,8 +1528,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,8 +1545,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1514,8 +1560,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1538,8 +1584,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1591,44 +1640,47 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-4200</v>
       </c>
       <c r="G26" s="3">
         <v>-4200</v>
       </c>
       <c r="H26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,44 +1696,47 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-4200</v>
       </c>
       <c r="G27" s="3">
         <v>-4200</v>
       </c>
       <c r="H27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,8 +1752,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1750,8 +1808,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1803,8 +1864,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1856,8 +1920,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1909,43 +1976,46 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1300</v>
+        <v>-2400</v>
       </c>
       <c r="E32" s="3">
-        <v>1100</v>
+        <v>-1400</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-1200</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1962,44 +2032,47 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-11700</v>
+        <v>-7300</v>
       </c>
       <c r="E33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-4200</v>
       </c>
       <c r="G33" s="3">
         <v>-4200</v>
       </c>
       <c r="H33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2015,8 +2088,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2068,44 +2144,47 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-11700</v>
+        <v>-7300</v>
       </c>
       <c r="E35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-4200</v>
       </c>
       <c r="G35" s="3">
         <v>-4200</v>
       </c>
       <c r="H35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,49 +2200,52 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2179,8 +2261,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2200,8 +2285,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2221,41 +2307,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E41" s="3">
         <v>28300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2274,8 +2361,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2327,23 +2417,26 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2356,8 +2449,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2380,31 +2473,34 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2433,41 +2529,44 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
-      </c>
-      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>900</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
-        <v>900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>700</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,41 +2585,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E46" s="3">
         <v>32100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2539,31 +2641,34 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2592,41 +2697,44 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E48" s="3">
         <v>19200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,37 +2753,40 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2698,8 +2809,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2751,8 +2865,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2804,8 +2921,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2816,16 +2936,16 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>1800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -2833,8 +2953,8 @@
       <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2851,14 +2971,17 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2910,41 +3033,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E54" s="3">
         <v>54800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2963,8 +3089,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2984,8 +3113,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3005,41 +3135,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3058,31 +3189,34 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3090,8 +3224,8 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -3111,41 +3245,44 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5400</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="F59" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
       <c r="G59" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="H59" s="3">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,41 +3301,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,31 +3357,34 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>29600</v>
+        <v>34600</v>
       </c>
       <c r="E61" s="3">
-        <v>22200</v>
+        <v>30700</v>
       </c>
       <c r="F61" s="3">
-        <v>200</v>
+        <v>23300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3270,41 +3413,44 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2700</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
-        <v>2800</v>
+        <v>1700</v>
       </c>
       <c r="F62" s="3">
-        <v>2800</v>
+        <v>1700</v>
       </c>
       <c r="G62" s="3">
-        <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>700</v>
+        <v>1700</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>700</v>
       </c>
       <c r="L62" s="3">
+        <v>700</v>
+      </c>
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3323,8 +3469,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3376,8 +3525,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3429,8 +3581,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3482,41 +3637,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>43700</v>
+        <v>42100</v>
       </c>
       <c r="E66" s="3">
-        <v>34900</v>
+        <v>40400</v>
       </c>
       <c r="F66" s="3">
-        <v>11200</v>
+        <v>32400</v>
       </c>
       <c r="G66" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H66" s="3">
         <v>3200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2700</v>
       </c>
       <c r="J66" s="3">
         <v>2700</v>
       </c>
       <c r="K66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,8 +3693,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3556,8 +3717,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3609,8 +3771,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3662,8 +3827,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3715,8 +3883,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3768,41 +3939,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-30800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-23800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-19700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3821,8 +3995,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3874,8 +4051,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3927,8 +4107,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3980,41 +4163,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4033,8 +4219,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4086,49 +4275,52 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4144,44 +4336,47 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-11700</v>
+        <v>-7300</v>
       </c>
       <c r="E81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-4200</v>
       </c>
       <c r="G81" s="3">
         <v>-4200</v>
       </c>
       <c r="H81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,8 +4392,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4218,37 +4416,38 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4271,8 +4470,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4324,8 +4526,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4377,8 +4582,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4430,8 +4638,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4483,8 +4694,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4536,44 +4750,47 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +4806,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4610,49 +4830,50 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4663,8 +4884,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4716,8 +4940,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4769,44 +4996,47 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +5052,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4843,31 +5076,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4896,8 +5130,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4949,8 +5186,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5002,8 +5242,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5055,44 +5298,47 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E100" s="3">
         <v>12200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8900</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5108,8 +5354,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5123,29 +5372,29 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>400</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5161,44 +5410,47 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E102" s="3">
         <v>4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5212,6 +5464,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>ASPI</t>
   </si>
@@ -656,75 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -740,26 +740,29 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -772,8 +775,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -796,26 +799,29 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
         <v>800</v>
-      </c>
-      <c r="E9" s="3">
-        <v>600</v>
       </c>
       <c r="F9" s="3">
         <v>600</v>
       </c>
       <c r="G9" s="3">
+        <v>600</v>
+      </c>
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -852,26 +858,29 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -908,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,47 +942,48 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,8 +1058,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1068,8 +1087,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1098,22 +1117,25 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1154,8 +1176,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,47 +1198,48 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,47 +1255,50 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,8 +1314,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,46 +1339,47 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>-100</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1363,47 +1396,50 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1455,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,14 +1470,14 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1451,8 +1490,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1475,47 +1514,50 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-4200</v>
       </c>
       <c r="H23" s="3">
         <v>-4200</v>
       </c>
       <c r="I23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J23" s="3">
         <v>-4300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,13 +1573,16 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1548,8 +1593,8 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1563,8 +1608,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1587,8 +1632,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,47 +1691,50 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-4200</v>
       </c>
       <c r="H26" s="3">
         <v>-4200</v>
       </c>
       <c r="I26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,47 +1750,50 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-4200</v>
       </c>
       <c r="H27" s="3">
         <v>-4200</v>
       </c>
       <c r="I27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1809,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1867,8 +1927,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,46 +2045,49 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>100</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -2035,47 +2104,50 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-4200</v>
       </c>
       <c r="H33" s="3">
         <v>-4200</v>
       </c>
       <c r="I33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-4300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,8 +2163,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,47 +2222,50 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-4200</v>
       </c>
       <c r="H35" s="3">
         <v>-4200</v>
       </c>
       <c r="I35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-4300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,52 +2281,55 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,8 +2345,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,44 +2393,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E41" s="3">
         <v>51600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2450,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2420,26 +2509,29 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2452,8 +2544,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2476,16 +2568,19 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="E44" s="3">
+        <v>100</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -2502,8 +2597,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2532,19 +2627,22 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -2558,18 +2656,18 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,44 +2686,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E46" s="3">
         <v>56100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,8 +2745,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2670,8 +2774,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2700,44 +2804,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E48" s="3">
         <v>24300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2756,40 +2863,43 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3300</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2812,8 +2922,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,13 +3040,16 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>1900</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -2939,16 +3058,16 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>1800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -2956,8 +3075,8 @@
       <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>100</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2974,14 +3093,17 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,44 +3158,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E54" s="3">
         <v>84100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>54800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3217,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,44 +3265,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,25 +3322,28 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
@@ -3219,7 +3352,7 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3227,8 +3360,8 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3248,44 +3381,47 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,44 +3440,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E60" s="3">
         <v>7400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,35 +3499,38 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E61" s="3">
         <v>34600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1300</v>
-      </c>
-      <c r="H61" s="3">
-        <v>600</v>
       </c>
       <c r="I61" s="3">
         <v>600</v>
       </c>
       <c r="J61" s="3">
+        <v>600</v>
+      </c>
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3416,16 +3558,19 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>1700</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>1700</v>
@@ -3433,8 +3578,8 @@
       <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>1700</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -3442,18 +3587,18 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>700</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>700</v>
       </c>
       <c r="M62" s="3">
+        <v>700</v>
+      </c>
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3617,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,44 +3794,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E66" s="3">
         <v>42100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2700</v>
       </c>
       <c r="K66" s="3">
         <v>2700</v>
       </c>
       <c r="L66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +3853,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3886,8 +4053,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,44 +4112,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-47000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-30800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-23800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-19700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-15500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4171,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,44 +4348,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E76" s="3">
         <v>38700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,8 +4407,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,52 +4466,55 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4339,47 +4530,50 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-4200</v>
       </c>
       <c r="H81" s="3">
         <v>-4200</v>
       </c>
       <c r="I81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-4300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4395,8 +4589,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,13 +4614,14 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -4443,14 +4641,14 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4473,8 +4671,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,47 +4966,50 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +5025,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,52 +5050,53 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4887,8 +5107,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,47 +5225,50 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5055,8 +5284,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,8 +5309,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5103,8 +5336,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5133,8 +5366,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,47 +5543,50 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E100" s="3">
         <v>32400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5602,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5366,38 +5614,38 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,47 +5661,50 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E102" s="3">
         <v>23300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,6 +5718,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
   <si>
     <t>ASPI</t>
   </si>
@@ -656,81 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -743,8 +745,14 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -755,20 +763,20 @@
         <v>1100</v>
       </c>
       <c r="F8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -778,11 +786,11 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -802,8 +810,14 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,17 +831,17 @@
         <v>600</v>
       </c>
       <c r="G9" s="3">
+        <v>800</v>
+      </c>
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>600</v>
+      </c>
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,8 +875,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,20 +893,20 @@
         <v>300</v>
       </c>
       <c r="F10" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
       </c>
       <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,8 +940,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -943,53 +969,55 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F12" s="3">
         <v>1400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>100</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
       </c>
       <c r="J12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
       </c>
       <c r="L12" s="3">
+        <v>300</v>
+      </c>
+      <c r="M12" s="3">
+        <v>200</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1002,8 +1030,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1061,8 +1095,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1090,11 +1130,11 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1120,29 +1160,35 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -1179,8 +1225,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1199,53 +1251,55 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F17" s="3">
         <v>8800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,53 +1312,59 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,8 +1377,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1340,52 +1406,54 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1399,53 +1467,59 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-9500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-7700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-8700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1458,8 +1532,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1473,16 +1553,16 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1493,11 +1573,11 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1517,53 +1597,59 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,31 +1662,37 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1611,11 +1703,11 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1635,8 +1727,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1694,53 +1792,59 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-75200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1753,53 +1857,59 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-11700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1812,8 +1922,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1871,8 +1987,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1930,8 +2052,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1989,8 +2117,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2048,52 +2182,58 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2107,53 +2247,59 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2166,8 +2312,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2225,53 +2377,59 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,58 +2442,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2348,8 +2512,14 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2371,8 +2541,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2394,50 +2566,52 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F41" s="3">
         <v>61900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>51600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>28300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>23900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2453,8 +2627,14 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2512,32 +2692,38 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
+        <v>700</v>
+      </c>
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,11 +2733,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2571,23 +2757,29 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>300</v>
+      </c>
+      <c r="F44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2600,11 +2792,11 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2630,8 +2822,14 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2641,14 +2839,14 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -2659,21 +2857,21 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2689,50 +2887,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>59000</v>
+      </c>
+      <c r="F46" s="3">
         <v>65700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>56100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>32100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>26200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,8 +2952,14 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2777,11 +2987,11 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2807,50 +3017,56 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F48" s="3">
         <v>23500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>24300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>19200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>15800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>12000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2866,46 +3082,52 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3200</v>
       </c>
       <c r="H49" s="3">
         <v>3300</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2925,8 +3147,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2984,8 +3212,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3043,8 +3277,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3052,37 +3292,37 @@
         <v>1900</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>1900</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
       <c r="J52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K52" s="3">
+        <v>200</v>
+      </c>
+      <c r="L52" s="3">
         <v>300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
+        <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -3096,14 +3336,20 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3161,50 +3407,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>135900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>90900</v>
+      </c>
+      <c r="F54" s="3">
         <v>94300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>84100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>54800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>45400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>27500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,8 +3472,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3243,8 +3501,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3266,50 +3526,52 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,49 +3587,55 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3384,50 +3652,56 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2600</v>
       </c>
       <c r="H59" s="3">
         <v>2400</v>
       </c>
       <c r="I59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,50 +3717,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F60" s="3">
         <v>7100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>8000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>2000</v>
       </c>
       <c r="L60" s="3">
         <v>1900</v>
       </c>
       <c r="M60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3502,41 +3782,47 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F61" s="3">
         <v>36100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>34600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>30700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>23300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3561,8 +3847,14 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3572,39 +3864,39 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1700</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>1700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3620,8 +3912,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3679,8 +3977,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3738,8 +4042,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3797,50 +4107,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>45100</v>
+      </c>
+      <c r="F66" s="3">
         <v>43200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>42100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>40400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>32400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,8 +4172,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3879,8 +4201,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3938,8 +4262,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3997,8 +4327,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4056,8 +4392,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4115,50 +4457,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-139700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-56200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-47000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-39700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-30800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-23800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-19700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-15500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-11200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-7600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-6200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-4300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4174,8 +4522,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4233,8 +4587,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4292,8 +4652,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4351,50 +4717,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F76" s="3">
         <v>47900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>38700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7400</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4410,8 +4782,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4469,58 +4847,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4533,53 +4917,59 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4592,8 +4982,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4615,20 +5011,22 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
@@ -4644,17 +5042,17 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4674,8 +5072,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4733,8 +5137,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4792,8 +5202,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4851,8 +5267,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4910,8 +5332,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4969,53 +5397,59 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5028,8 +5462,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5051,58 +5491,60 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5552,14 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5169,8 +5617,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5228,53 +5682,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5287,8 +5747,14 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5310,8 +5776,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5339,11 +5807,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5369,8 +5837,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5428,8 +5902,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5487,8 +5967,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5546,53 +6032,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
         <v>17700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>32400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>12200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>20300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>8900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3800</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5605,8 +6097,14 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5614,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -5626,32 +6124,32 @@
         <v>-100</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5664,53 +6162,59 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F102" s="3">
         <v>10300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>23300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5721,6 +6225,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="92">
   <si>
     <t>ASPI</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,19 +756,25 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F8" s="3">
         <v>4900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1100</v>
       </c>
       <c r="G8" s="3">
         <v>1200</v>
@@ -776,20 +783,20 @@
         <v>1100</v>
       </c>
       <c r="I8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -799,11 +806,11 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -823,19 +830,25 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F9" s="3">
         <v>4500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>800</v>
       </c>
       <c r="G9" s="3">
         <v>600</v>
@@ -847,17 +860,17 @@
         <v>600</v>
       </c>
       <c r="J9" s="3">
+        <v>800</v>
+      </c>
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
+        <v>600</v>
+      </c>
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,19 +904,25 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F10" s="3">
         <v>400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>300</v>
       </c>
       <c r="G10" s="3">
         <v>600</v>
@@ -912,20 +931,20 @@
         <v>300</v>
       </c>
       <c r="I10" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J10" s="3">
         <v>300</v>
       </c>
       <c r="K10" s="3">
+        <v>400</v>
+      </c>
+      <c r="L10" s="3">
+        <v>300</v>
+      </c>
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +978,14 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,62 +1010,64 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F12" s="3">
         <v>3100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>100</v>
       </c>
       <c r="L12" s="3">
         <v>200</v>
       </c>
       <c r="M12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
       </c>
       <c r="O12" s="3">
+        <v>300</v>
+      </c>
+      <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1080,14 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,16 +1154,22 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-15200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1159,11 +1198,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1189,38 +1228,44 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1257,8 +1302,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,62 +1331,64 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F17" s="3">
         <v>19900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>13200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,62 +1401,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-15000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-8000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-5400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-7500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1475,14 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,61 +1507,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>63900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1510,62 +1577,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-14200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-75400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-9500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-8700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,16 +1651,22 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>1700</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1602,16 +1681,16 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>100</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1622,11 +1701,11 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1646,62 +1725,68 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-12800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-75100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-9100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,40 +1799,46 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1758,11 +1849,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1782,8 +1873,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,62 +1947,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-75200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-8500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,62 +2021,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-75100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-8400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-11700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2095,14 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,13 +2169,19 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2122,8 +2243,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2317,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,61 +2391,67 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-63900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2326,62 +2465,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-75100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2539,14 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,62 +2613,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-75100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2687,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2766,14 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2798,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,59 +2826,61 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>207300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>285600</v>
+      </c>
+      <c r="F41" s="3">
         <v>113900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>67700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>56000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>61900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>51600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>28300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,20 +2896,26 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>49100</v>
+      </c>
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2791,41 +2970,47 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>51700</v>
+      </c>
+      <c r="F43" s="3">
         <v>50100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>31000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
-        <v>700</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,11 +3020,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2859,8 +3044,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2868,23 +3059,23 @@
         <v>1400</v>
       </c>
       <c r="E44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2897,11 +3088,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2927,20 +3118,26 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F45" s="3">
         <v>7500</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2948,13 +3145,13 @@
         <v>3</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2965,21 +3162,21 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,59 +3192,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>308700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>399900</v>
+      </c>
+      <c r="F46" s="3">
         <v>174000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>101600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>59000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>65700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>56100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>32100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>26200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3600</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,20 +3266,26 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>47300</v>
+      </c>
+      <c r="F47" s="3">
         <v>6300</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,11 +3310,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3131,59 +3340,65 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>224900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F48" s="3">
         <v>31900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>28600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>26400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>23500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>24300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>19200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>15800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>12000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>8700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>9100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,55 +3414,61 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F49" s="3">
         <v>8000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3500</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3200</v>
       </c>
       <c r="K49" s="3">
         <v>3300</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="M49" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3267,8 +3488,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3562,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,55 +3636,61 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F52" s="3">
         <v>5100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2100</v>
       </c>
       <c r="G52" s="3">
         <v>1900</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="I52" s="3">
-        <v>200</v>
+        <v>1900</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
       </c>
       <c r="K52" s="3">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N52" s="3">
+        <v>200</v>
+      </c>
+      <c r="O52" s="3">
         <v>300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
+        <v>100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3465,14 +3704,20 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,59 +3784,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>587700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>498000</v>
+      </c>
+      <c r="F54" s="3">
         <v>225900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>135900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>90900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>94300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>84100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>54800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>45400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>27500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>12500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>9500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>10000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3858,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3890,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,59 +3918,61 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,58 +3988,64 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F58" s="3">
         <v>13000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3795,59 +4062,65 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2600</v>
       </c>
       <c r="K59" s="3">
         <v>2400</v>
       </c>
       <c r="L59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,59 +4136,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F60" s="3">
         <v>28300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>8200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>2000</v>
       </c>
       <c r="O60" s="3">
         <v>1900</v>
       </c>
       <c r="P60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R60" s="3">
         <v>2500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1800</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,50 +4210,56 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>207600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>202300</v>
+      </c>
+      <c r="F61" s="3">
         <v>100600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>100700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>37000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>36100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>34600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>30700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>23300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3999,19 +4284,25 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+      <c r="F62" s="3">
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -4019,39 +4310,39 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1700</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>1700</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4358,14 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4432,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4506,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,59 +4580,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>288700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>235100</v>
+      </c>
+      <c r="F66" s="3">
         <v>129300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>107600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>45100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>43200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>42100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>40400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>32400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4654,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4686,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4756,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4830,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4904,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,59 +4978,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-238500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-231300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-152600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-139700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-64600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-56200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-47000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-39700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-30800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-23800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-19700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-15500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-11200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-7600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-4300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +5052,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +5126,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5200,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,59 +5274,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>289000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>204200</v>
+      </c>
+      <c r="F76" s="3">
         <v>74100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>25200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>42500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>47900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>38700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>16300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>10200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7400</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5348,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5422,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,62 +5501,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-75100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5575,14 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,8 +5607,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5221,20 +5618,20 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -5250,17 +5647,17 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -5280,8 +5677,14 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5751,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5825,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5899,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5973,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,62 +6047,68 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-8900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +6121,14 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,67 +6153,69 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -5782,8 +6223,14 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6297,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,62 +6371,68 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-75200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-31700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5986,8 +6445,14 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6477,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6050,11 +6517,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6080,8 +6547,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6621,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6695,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,62 +6769,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>264100</v>
+      </c>
+      <c r="F100" s="3">
         <v>56700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>51000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>17700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>32400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>12200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>20300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>8900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>4500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>3800</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>2200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,28 +6843,34 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -6382,32 +6879,32 @@
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6420,62 +6917,68 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>171600</v>
+      </c>
+      <c r="F102" s="3">
         <v>46300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>11700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>23300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>16000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>5600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6989,12 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
